--- a/109到114年度 五股已完工設施盤點.xlsx
+++ b/109到114年度 五股已完工設施盤點.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\03-農業發展與水資源保育\04-個人工作備份\杜柏叡\農水設計組\02-五股\五股灌溉系統網站\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\03-農業發展與水資源保育\01-執行中專案\09-七星管理處_五股坑溪擴大灌溉服務推動暨觀音坑溪補充設計推動計畫\10-坑溝取水設施盤點資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D8CF58-412E-4726-9A51-857BAE7CF7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7156D93A-3ADA-4459-A209-0733CC8E1693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2862070-784E-45A9-AD87-022E2482076D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2862070-784E-45A9-AD87-022E2482076D}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="1" r:id="rId1"/>
     <sheet name="缺失樣態" sheetId="2" r:id="rId2"/>
     <sheet name="接管名冊及電話" sheetId="3" r:id="rId3"/>
-    <sheet name="設施照片" sheetId="4" r:id="rId4"/>
+    <sheet name="五股農民民單" sheetId="5" r:id="rId4"/>
+    <sheet name="設施尺寸" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">總表!$A$1:$X$56</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="523">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -2270,18 +2271,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宣導或名牌提供聯絡資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒廢設施</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>評估移置他處或取消</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>現場無接管戶資訊</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2334,18 +2323,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>修復</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>安全性-行走動線</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>設置護欄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>無動力揚水進水不穩定</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2355,10 +2336,6 @@
   </si>
   <si>
     <t>斷管</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>崩1-2、</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2874,14 +2851,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中B5鋼構橋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中W3(再確認)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>崩B6(已通知改善5/9前改善完成)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3317,22 +3286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>出水口過低，淤砂影響</t>
-  </si>
-  <si>
-    <t>下管改接上管</t>
-  </si>
-  <si>
-    <t>1.出水口過低，淤砂影響
-2.現場無接管戶資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.下管改接上管
-2.箱體編號(貼在明顯處，不一定在箱體)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3405,11 +3358,925 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>維護管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>結構改善</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳衍至錯接崩4-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由崩4-7接管至陳錦輝堂哥農地</t>
+  </si>
+  <si>
+    <t>取崩1-2溢流水接至九天玄女宮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取崩B2溢流水串接崩B3(跨區調度)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中W2溢流水串接至中B4，再將中B4與溢流水往下游送</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>應接回崩4-6</t>
+  </si>
+  <si>
+    <t>延管工程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>維護宣導</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規劃管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常流水的緣故，中B5接管率不佳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3"-&gt;3/4"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/4"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4"+2"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2"-&gt;3/4"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2"-&gt; 1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1"-&gt;3/4"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2"-&gt; 3/4"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2"-&gt; 1.5"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3"+2"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3"-&gt;2"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5"-&gt;3/4" </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灌溉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重力/動力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯絡方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中直坑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳慶華</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坑溝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中W1~W3在慶華大哥家後面，109~113年度中直坑坑溝取水及智慧灌溉配合人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳根永</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動力抽水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W5 末端、凌雲路三段及中直路交叉口巷子內、崩山坑及中直坑下游協助推動的人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>廖正陽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中直路這一帶的班長，不在設施受益範圍內</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坑溝、帆布蓄水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重力&amp;動力抽水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0928201293</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中W5旁的接管農民，認同擴大灌溉服務，有申請過田間管路補助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林國明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坑溝、水井</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林國順的弟弟，中W4接管戶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林世文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林國明兒子，中W3接管戶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳玉山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒有資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>農會推舉的五股地區維護管理協助人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳汪鏗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代稱：小狗農戶、中W1接管戶、農舍在中W2旁、文傑副座常說的有一對夫妻倆有跟七星道謝，也贊同坑溝取水的就是他們</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳志長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湧泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不清楚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0988761994</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2年前有提到他老家附近有一處湧泉想改善可供大家使用，但後來聯絡不上，經在地協助打聽好像是打消念頭了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>易炳南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0915802258</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>農地在中直坑溪未來規劃的串聯處附近</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0912243257</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中直坑有農地(接中W1水源)、崩山坑是親戚的地他負責耕作照顧(接崩W4水源)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩山坑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伍春香</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W1下游農民、主要在幫崩山跟中直坑(九天玄女宮附近的地主代耕農地)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃三珊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張海桐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W3潛在受益戶，他希望崩W2溢流水接到崩W3，這樣他才願意接管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳信夫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>古厝在崩W4旁、崩山坑溪中上游的主要推動人、年紀大有點重聽、後來比較常找他姪子陳錦盛幫忙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳致逸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>八里農會、陳信夫的小兒子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳錦盛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W3接管戶、崩山坑溪主要協助我們推動的人、主動幫忙維護管理崩W3、資誠影片有找他訪談</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W4土地公廟下游潛在延伸用戶、農地在崩山坑溪下游右岸、他已經跟地主喬好了，希望七星可以沿管到他那邊，並幫忙放一顆蓄水池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李曜文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林研熙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W1下游農民，農地是地主租給他們耕作的，有在崩B1-2接管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳福</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩山坑的前班長，農地在崩山坑溪下游左岸，崩W4有一管預留要延伸給他，但他興致缺缺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戴榮讓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W4接管戶之一，有在崩山土地公廟上游鐵皮屋旁分一管給他接，農會代表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳永輝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩W4接管戶之一，有在崩山土地公廟上游不遠處的公廟後方分一管給他接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無動力揚水配合人、土地是陳文章的(天山鄉土雞城老闆0937983076，他跟五股坑溪的鄰長同名、但不同人)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳信元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀音坑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林青豊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0939943890</t>
+  </si>
+  <si>
+    <t>觀W1潛在受益戶，農地是375的租地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楊明樺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0939506725</t>
+  </si>
+  <si>
+    <t>凌雲寺下游農地，訪談時表示這邊都老人了沒有人要接手，再做也沒幾年，不建議投入資源再這附近，之前楊海塗來推農村再生時這一代農民也都興致缺缺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五股坑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳文章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0920422052</t>
+  </si>
+  <si>
+    <t>五股坑溪第一座坑溝取水示範區，五龍里14鄰鄰長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0920-422-052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-22938692</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳伯凱</t>
+  </si>
+  <si>
+    <t>坑溝、湧泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0910127865</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五股坑溪上游青農，家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳燕山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0916039288</t>
+  </si>
+  <si>
+    <t>五龍里里長、他覺得坑溝取水設施對這邊幫助不大，但要推他不反對，沒有很想幫忙，只叫我們去找陳文章鄰長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>壟鉤坑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳宏基</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湧泉取水、水源在私有地，是祖先與地主口頭談好使用至今，有自己的田間管路、對智慧灌溉有興趣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張朴仁</t>
+  </si>
+  <si>
+    <t>0933050925</t>
+  </si>
+  <si>
+    <t>張國炎</t>
+  </si>
+  <si>
+    <t>太久忘了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0989996582</t>
+  </si>
+  <si>
+    <t>五股農會現任理事長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御史坑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>涂泰郎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湧泉、水井</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御史坑中游農民，有在私有湧泉接管灌溉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葉義雄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水井</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御史坑上游農民，自農地旁水井抽水灌溉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄭義信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太久沒聯絡忘記了，只記得在御史路上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳永堅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林炳祥</t>
+  </si>
+  <si>
+    <t>雨水儲留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0936137606</t>
+  </si>
+  <si>
+    <t>御史坑下游南側農民，農地在稜線上沒有水源只能靠雨水儲留跟看天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>許水泉</t>
+  </si>
+  <si>
+    <t>0936156996</t>
+  </si>
+  <si>
+    <t>御史坑下游北側農民，農地在稜線上沒有水源只能靠雨水儲留跟看天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳林玉雲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御史坑下游農民，農地內有湧泉、水井</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳振卿</t>
+  </si>
+  <si>
+    <t>御史坑下游農民，從湧泉接管灌溉，不得已時才從御史坑溪下游抽水(水質不好)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旗竿湖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳國池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埤塘、水井</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳澤民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳國池的弟弟，對田間管路有興趣，有自己的噴灌園區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳明順</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太久沒聯絡忘記了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳永田</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在班長、住在旗竿湖旁邊那一間白色屋子裡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>詹木火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳文棋</t>
+  </si>
+  <si>
+    <t>0926878290</t>
+  </si>
+  <si>
+    <t>御史坑最上游埤塘地主，兩兄弟都願意提供溢流水或埤塘給周遭的人用，但前提是希望能改善埤塘高低差問題並將道路側溝水源截到埤塘內</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳煌棋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>詹舜翔</t>
+  </si>
+  <si>
+    <t>0933751991</t>
+  </si>
+  <si>
+    <t>楊榮祿</t>
+  </si>
+  <si>
+    <t>0933751992</t>
+  </si>
+  <si>
+    <t>林志忠</t>
+  </si>
+  <si>
+    <t>0917878253</t>
+  </si>
+  <si>
+    <t>他老婆帶我們看水源的，他本人沒有出面，那邊水井以民生為主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河溝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄭仕揆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埤塘、湧泉、水井</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0932245409</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水保局早期做的埤塘引水，但分水設施在私有地內且距離公有地跟道路太遠，所以沒人接。
+有湧泉、水井等資源願意共享，希望公布來改善大家一起用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外寮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林進煙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埤塘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>農會理事、以前的主要聯絡人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡文亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>農會代表、外寮P1埤塘地主之一、現主要聯絡人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林美惠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前農會推廣部主任、跟其他人在外寮合租土地耕作菜園</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上游設施</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下游設施</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管徑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高程差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>距離</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-8</t>
+  </si>
+  <si>
+    <t>崩支5-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩支5-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩支5-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩支6-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩支6-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩支6-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩支6-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中W1、中W2、中W4、中W5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩4-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>將中B5移置下游並銜接B4溢流水;鋼構橋移至他處或移除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中B5及中B5鋼構橋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.出水口過低，淤砂影響
+2.現場無接管戶資訊
+3.球閥不易開啟
+4.取水箱無活動式開孔
+5.箱體導水坡面破損</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.下管改接上管
+2.箱體編號(貼在明顯處，不一定在箱體)
+3.把手延伸管
+4.修改為活動式
+5.將破損處修復</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.設置安全扶手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.排砂閥使用之安全性
+2.行走動線之安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.設置安全扶手
+2.設置安全護欄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.出水口過低，淤砂影響
+2.取水箱無活動式開孔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.115 5月現場無接管
+2.取水箱無活動式開孔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.下管改接上管
+2.修改為活動式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.宣導或掛設名牌提供聯絡資訊
+2.修改為活動式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣導或掛設名牌提供聯絡資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請廠商改善</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請廠商加裝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修復破損部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>釐清原因，視需求改善</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.115 5月現場無接管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.宣導或掛設名牌提供聯絡資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.出水口過低，淤砂影響
+2.取水箱難以到達</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.取水箱無活動式開孔
+2.取水箱難以到達</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.下管改接上管
+2.設置塑膠包覆踏接或活動爬梯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.修改為活動式
+2.設置塑膠包覆踏接或活動爬梯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.115 4月現場分水頭斷掉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.釐清原因，視需求改善</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.三角架焊接斷裂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.改直立式角鋼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設置安全護欄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.分水鞍使用之安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.蓄水塔下方無排砂管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.請廠商加裝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.出水管末端排砂管錯接
+2.溢流管對衝管線易造成脫落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.請廠商改善
+2.裝設斜角彎管避免對衝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.將中B5移置下游並銜接B4溢流水
+2.鋼構橋移至他處或移除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.接管率不佳
+2.設施荒廢</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3417,7 +4284,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3521,8 +4388,30 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3586,6 +4475,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3747,7 +4654,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3871,8 +4778,41 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3955,35 +4895,86 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3992,6 +4983,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FFFF66FF"/>
+      <color rgb="FFCC66FF"/>
+      <color rgb="FFFF00FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4337,46 +5336,46 @@
         <v>105</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G1" s="25" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>106</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="Q1" s="18" t="s">
         <v>10</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="S1" s="37" t="s">
         <v>101</v>
@@ -4388,12 +5387,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="55.5">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:38" ht="138.75">
+      <c r="A2" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
@@ -4407,7 +5406,7 @@
         <v>183.78</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I2" s="21"/>
       <c r="J2" s="22"/>
@@ -4426,22 +5425,22 @@
       <c r="Q2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="41" t="s">
-        <v>294</v>
-      </c>
-      <c r="S2" s="41" t="s">
-        <v>295</v>
+      <c r="R2" s="105" t="s">
+        <v>491</v>
+      </c>
+      <c r="S2" s="105" t="s">
+        <v>492</v>
       </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A3" s="42"/>
+    <row r="3" spans="1:38" ht="55.5">
+      <c r="A3" s="53"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D3" s="24"/>
       <c r="E3" s="24">
@@ -4471,17 +5470,21 @@
       <c r="Q3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
+      <c r="R3" s="105" t="s">
+        <v>494</v>
+      </c>
+      <c r="S3" s="105" t="s">
+        <v>495</v>
+      </c>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
     </row>
     <row r="4" spans="1:38" s="4" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A4" s="43"/>
+      <c r="A4" s="54"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E4" s="24">
         <v>292103</v>
@@ -4493,7 +5496,7 @@
         <v>179.19</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I4" s="21"/>
       <c r="J4" s="22">
@@ -4517,10 +5520,12 @@
       <c r="Q4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="S4" s="37"/>
+      <c r="R4" s="106" t="s">
+        <v>505</v>
+      </c>
+      <c r="S4" s="106" t="s">
+        <v>506</v>
+      </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="1"/>
@@ -4541,8 +5546,8 @@
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
     </row>
-    <row r="5" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A5" s="45"/>
+    <row r="5" spans="1:38" ht="55.5">
+      <c r="A5" s="56"/>
       <c r="B5" s="24" t="s">
         <v>16</v>
       </c>
@@ -4575,17 +5580,17 @@
       <c r="Q5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="S5" s="37" t="s">
-        <v>293</v>
+      <c r="R5" s="105" t="s">
+        <v>496</v>
+      </c>
+      <c r="S5" s="105" t="s">
+        <v>498</v>
       </c>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
     <row r="6" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A6" s="42"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24" t="s">
         <v>18</v>
@@ -4618,23 +5623,23 @@
       <c r="Q6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
+      <c r="R6" s="106"/>
+      <c r="S6" s="106"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A7" s="43"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G7" s="24">
         <v>166.15</v>
@@ -4662,13 +5667,13 @@
       <c r="Q7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A8" s="45"/>
+    <row r="8" spans="1:38" ht="55.5">
+      <c r="A8" s="56"/>
       <c r="B8" s="24" t="s">
         <v>22</v>
       </c>
@@ -4701,17 +5706,17 @@
       <c r="Q8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R8" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="S8" s="37" t="s">
-        <v>293</v>
+      <c r="R8" s="105" t="s">
+        <v>507</v>
+      </c>
+      <c r="S8" s="105" t="s">
+        <v>509</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A9" s="42"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24" t="s">
         <v>24</v>
@@ -4744,13 +5749,13 @@
       <c r="Q9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
+      <c r="R9" s="106"/>
+      <c r="S9" s="106"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
     <row r="10" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A10" s="43"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
       <c r="D10" s="24" t="s">
@@ -4781,20 +5786,20 @@
         <v>6</v>
       </c>
       <c r="N10" s="29" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="O10" s="20"/>
       <c r="P10" s="20"/>
       <c r="Q10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
+      <c r="R10" s="106"/>
+      <c r="S10" s="106"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A11" s="45"/>
+    <row r="11" spans="1:38" ht="55.5">
+      <c r="A11" s="56"/>
       <c r="B11" s="24" t="s">
         <v>26</v>
       </c>
@@ -4827,13 +5832,17 @@
       <c r="Q11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
+      <c r="R11" s="105" t="s">
+        <v>508</v>
+      </c>
+      <c r="S11" s="105" t="s">
+        <v>510</v>
+      </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
     <row r="12" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A12" s="42"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="24"/>
       <c r="C12" s="24" t="s">
         <v>29</v>
@@ -4866,20 +5875,24 @@
       <c r="Q12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
+      <c r="R12" s="106" t="s">
+        <v>513</v>
+      </c>
+      <c r="S12" s="106" t="s">
+        <v>514</v>
+      </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
     <row r="13" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
       <c r="D13" s="24" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F13" s="24">
         <v>2779125</v>
@@ -4903,20 +5916,20 @@
         <v>4</v>
       </c>
       <c r="N13" s="29" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="20"/>
       <c r="Q13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
+      <c r="R13" s="106"/>
+      <c r="S13" s="106"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A14" s="45"/>
+    <row r="14" spans="1:38" ht="55.5">
+      <c r="A14" s="56"/>
       <c r="B14" s="24" t="s">
         <v>32</v>
       </c>
@@ -4949,15 +5962,17 @@
       <c r="Q14" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R14" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="S14" s="37"/>
+      <c r="R14" s="105" t="s">
+        <v>497</v>
+      </c>
+      <c r="S14" s="105" t="s">
+        <v>499</v>
+      </c>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A15" s="42"/>
+    <row r="15" spans="1:38" ht="55.5">
+      <c r="A15" s="53"/>
       <c r="B15" s="24"/>
       <c r="C15" s="24" t="s">
         <v>33</v>
@@ -4990,13 +6005,17 @@
       <c r="Q15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R15" s="37"/>
-      <c r="S15" s="37"/>
+      <c r="R15" s="105" t="s">
+        <v>522</v>
+      </c>
+      <c r="S15" s="105" t="s">
+        <v>521</v>
+      </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
     <row r="16" spans="1:38" ht="32.1" customHeight="1">
-      <c r="A16" s="43"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
       <c r="D16" s="24" t="s">
@@ -5024,23 +6043,23 @@
         <v>0</v>
       </c>
       <c r="M16" s="30" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N16" s="29" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="20"/>
       <c r="Q16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
+      <c r="R16" s="106"/>
+      <c r="S16" s="106"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="56" t="s">
         <v>36</v>
       </c>
       <c r="B17" s="24" t="s">
@@ -5075,13 +6094,13 @@
       <c r="Q17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
+      <c r="R17" s="106"/>
+      <c r="S17" s="106"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A18" s="42"/>
+      <c r="A18" s="53"/>
       <c r="C18" s="24" t="s">
         <v>39</v>
       </c>
@@ -5113,13 +6132,13 @@
       <c r="Q18" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
+      <c r="R18" s="106"/>
+      <c r="S18" s="106"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A19" s="42"/>
+      <c r="A19" s="53"/>
       <c r="C19" s="24" t="s">
         <v>41</v>
       </c>
@@ -5151,13 +6170,13 @@
       <c r="Q19" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
+      <c r="R19" s="106"/>
+      <c r="S19" s="106"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A20" s="42"/>
+      <c r="A20" s="53"/>
       <c r="C20" s="24"/>
       <c r="D20" s="24" t="s">
         <v>42</v>
@@ -5194,13 +6213,13 @@
       <c r="Q20" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R20" s="37"/>
-      <c r="S20" s="37"/>
+      <c r="R20" s="106"/>
+      <c r="S20" s="106"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A21" s="42"/>
+      <c r="A21" s="53"/>
       <c r="C21" s="24"/>
       <c r="D21" s="24" t="s">
         <v>45</v>
@@ -5237,13 +6256,17 @@
       <c r="Q21" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R21" s="37"/>
-      <c r="S21" s="37"/>
+      <c r="R21" s="106" t="s">
+        <v>511</v>
+      </c>
+      <c r="S21" s="106" t="s">
+        <v>512</v>
+      </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A22" s="43"/>
+      <c r="A22" s="54"/>
       <c r="C22" s="24"/>
       <c r="D22" s="24" t="s">
         <v>47</v>
@@ -5280,15 +6303,13 @@
       <c r="Q22" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R22" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="S22" s="37"/>
+      <c r="R22" s="106"/>
+      <c r="S22" s="106"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A23" s="45"/>
+      <c r="A23" s="56"/>
       <c r="B23" s="24" t="s">
         <v>49</v>
       </c>
@@ -5321,8 +6342,8 @@
       <c r="Q23" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R23" s="37"/>
-      <c r="S23" s="37"/>
+      <c r="R23" s="106"/>
+      <c r="S23" s="106"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="X23" s="1" t="s">
@@ -5330,7 +6351,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A24" s="42"/>
+      <c r="A24" s="53"/>
       <c r="C24" s="24" t="s">
         <v>50</v>
       </c>
@@ -5362,13 +6383,13 @@
       <c r="Q24" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R24" s="37"/>
-      <c r="S24" s="37"/>
+      <c r="R24" s="106"/>
+      <c r="S24" s="106"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A25" s="42"/>
+      <c r="A25" s="53"/>
       <c r="C25" s="24"/>
       <c r="D25" s="24" t="s">
         <v>52</v>
@@ -5405,13 +6426,13 @@
       <c r="Q25" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R25" s="37"/>
-      <c r="S25" s="37"/>
+      <c r="R25" s="106"/>
+      <c r="S25" s="106"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A26" s="42"/>
+      <c r="A26" s="53"/>
       <c r="C26" s="24"/>
       <c r="D26" s="24" t="s">
         <v>54</v>
@@ -5448,13 +6469,13 @@
       <c r="Q26" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R26" s="37"/>
-      <c r="S26" s="37"/>
+      <c r="R26" s="106"/>
+      <c r="S26" s="106"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A27" s="42"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="24" t="s">
         <v>55</v>
       </c>
@@ -5487,13 +6508,13 @@
       <c r="Q27" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R27" s="37"/>
-      <c r="S27" s="37"/>
+      <c r="R27" s="106"/>
+      <c r="S27" s="106"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A28" s="42"/>
+      <c r="A28" s="53"/>
       <c r="C28" s="24" t="s">
         <v>56</v>
       </c>
@@ -5525,13 +6546,13 @@
       <c r="Q28" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
+      <c r="R28" s="106"/>
+      <c r="S28" s="106"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
     <row r="29" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A29" s="42"/>
+      <c r="A29" s="53"/>
       <c r="C29" s="24"/>
       <c r="D29" s="24" t="s">
         <v>57</v>
@@ -5568,20 +6589,20 @@
       <c r="Q29" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
+      <c r="R29" s="106"/>
+      <c r="S29" s="106"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
     <row r="30" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A30" s="42"/>
+      <c r="A30" s="53"/>
       <c r="B30" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
       <c r="E30" s="24" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="F30" s="24">
         <v>2779185</v>
@@ -5607,19 +6628,19 @@
       <c r="Q30" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R30" s="37"/>
-      <c r="S30" s="37"/>
+      <c r="R30" s="106"/>
+      <c r="S30" s="106"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A31" s="42"/>
+      <c r="A31" s="53"/>
       <c r="C31" s="24" t="s">
         <v>60</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F31" s="24">
         <v>2779165</v>
@@ -5645,19 +6666,19 @@
       <c r="Q31" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
+      <c r="R31" s="106"/>
+      <c r="S31" s="106"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
     <row r="32" spans="1:24" ht="32.1" customHeight="1">
-      <c r="A32" s="42"/>
+      <c r="A32" s="53"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24" t="s">
         <v>61</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F32" s="24">
         <v>2779164</v>
@@ -5688,13 +6709,13 @@
       <c r="Q32" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R32" s="37"/>
-      <c r="S32" s="37"/>
+      <c r="R32" s="106"/>
+      <c r="S32" s="106"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
     </row>
     <row r="33" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A33" s="42"/>
+      <c r="A33" s="53"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24" t="s">
         <v>62</v>
@@ -5731,13 +6752,13 @@
       <c r="Q33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R33" s="37"/>
-      <c r="S33" s="37"/>
+      <c r="R33" s="106"/>
+      <c r="S33" s="106"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
     <row r="34" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A34" s="42"/>
+      <c r="A34" s="53"/>
       <c r="C34" s="24"/>
       <c r="D34" s="24" t="s">
         <v>64</v>
@@ -5774,13 +6795,13 @@
       <c r="Q34" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R34" s="37"/>
-      <c r="S34" s="37"/>
+      <c r="R34" s="106"/>
+      <c r="S34" s="106"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
     <row r="35" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A35" s="42"/>
+      <c r="A35" s="53"/>
       <c r="C35" s="24"/>
       <c r="D35" s="24" t="s">
         <v>66</v>
@@ -5817,15 +6838,15 @@
       <c r="Q35" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="S35" s="37"/>
+      <c r="R35" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="S35" s="106"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
     <row r="36" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A36" s="42"/>
+      <c r="A36" s="53"/>
       <c r="C36" s="24"/>
       <c r="D36" s="24" t="s">
         <v>68</v>
@@ -5862,13 +6883,13 @@
       <c r="Q36" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R36" s="37"/>
-      <c r="S36" s="37"/>
+      <c r="R36" s="106"/>
+      <c r="S36" s="106"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
     </row>
     <row r="37" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A37" s="42"/>
+      <c r="A37" s="53"/>
       <c r="C37" s="24"/>
       <c r="D37" s="24" t="s">
         <v>70</v>
@@ -5905,19 +6926,23 @@
       <c r="Q37" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R37" s="37"/>
-      <c r="S37" s="37"/>
+      <c r="R37" s="106" t="s">
+        <v>516</v>
+      </c>
+      <c r="S37" s="106" t="s">
+        <v>493</v>
+      </c>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
     </row>
     <row r="38" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A38" s="42"/>
+      <c r="A38" s="53"/>
       <c r="C38" s="24"/>
       <c r="D38" s="24" t="s">
         <v>71</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F38" s="24">
         <v>2778802</v>
@@ -5948,20 +6973,24 @@
       <c r="Q38" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="37"/>
+      <c r="R38" s="106" t="s">
+        <v>516</v>
+      </c>
+      <c r="S38" s="106" t="s">
+        <v>493</v>
+      </c>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
     <row r="39" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A39" s="42"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="24" t="s">
         <v>73</v>
       </c>
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F39" s="24">
         <v>2778906</v>
@@ -5987,15 +7016,15 @@
       <c r="Q39" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R39" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="S39" s="37"/>
+      <c r="R39" s="106" t="s">
+        <v>157</v>
+      </c>
+      <c r="S39" s="106"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A40" s="42"/>
+    <row r="40" spans="1:21" ht="55.5">
+      <c r="A40" s="53"/>
       <c r="C40" s="24" t="s">
         <v>75</v>
       </c>
@@ -6004,7 +7033,7 @@
         <v>292672</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="G40" s="24">
         <v>89.32</v>
@@ -6027,13 +7056,17 @@
       <c r="Q40" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="37"/>
+      <c r="R40" s="105" t="s">
+        <v>519</v>
+      </c>
+      <c r="S40" s="105" t="s">
+        <v>520</v>
+      </c>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
     </row>
     <row r="41" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A41" s="42"/>
+      <c r="A41" s="53"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24" t="s">
         <v>77</v>
@@ -6070,13 +7103,13 @@
       <c r="Q41" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
+      <c r="R41" s="106"/>
+      <c r="S41" s="106"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
     </row>
     <row r="42" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A42" s="42"/>
+      <c r="A42" s="53"/>
       <c r="C42" s="24"/>
       <c r="D42" s="24" t="s">
         <v>78</v>
@@ -6113,13 +7146,13 @@
       <c r="Q42" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R42" s="37"/>
-      <c r="S42" s="37"/>
+      <c r="R42" s="106"/>
+      <c r="S42" s="106"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
     </row>
     <row r="43" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A43" s="42"/>
+      <c r="A43" s="53"/>
       <c r="C43" s="24"/>
       <c r="D43" s="24" t="s">
         <v>80</v>
@@ -6156,13 +7189,13 @@
       <c r="Q43" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R43" s="37"/>
-      <c r="S43" s="37"/>
+      <c r="R43" s="106"/>
+      <c r="S43" s="106"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
     </row>
     <row r="44" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A44" s="42"/>
+      <c r="A44" s="53"/>
       <c r="C44" s="24"/>
       <c r="D44" s="24" t="s">
         <v>82</v>
@@ -6199,23 +7232,23 @@
       <c r="Q44" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R44" s="37"/>
-      <c r="S44" s="37"/>
+      <c r="R44" s="106"/>
+      <c r="S44" s="106"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
     </row>
     <row r="45" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A45" s="42"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="24" t="s">
         <v>83</v>
       </c>
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
       <c r="E45" s="24" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G45" s="24">
         <v>75</v>
@@ -6238,13 +7271,13 @@
       <c r="Q45" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R45" s="37"/>
-      <c r="S45" s="37"/>
+      <c r="R45" s="106"/>
+      <c r="S45" s="106"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
     </row>
     <row r="46" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A46" s="42"/>
+      <c r="A46" s="53"/>
       <c r="C46" s="24" t="s">
         <v>85</v>
       </c>
@@ -6276,13 +7309,17 @@
       <c r="Q46" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R46" s="37"/>
-      <c r="S46" s="37"/>
+      <c r="R46" s="106" t="s">
+        <v>517</v>
+      </c>
+      <c r="S46" s="106" t="s">
+        <v>518</v>
+      </c>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
     </row>
     <row r="47" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A47" s="42"/>
+      <c r="A47" s="53"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24" t="s">
         <v>86</v>
@@ -6319,13 +7356,13 @@
       <c r="Q47" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
+      <c r="R47" s="106"/>
+      <c r="S47" s="106"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
     </row>
     <row r="48" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A48" s="42"/>
+      <c r="A48" s="53"/>
       <c r="C48" s="24"/>
       <c r="D48" s="24" t="s">
         <v>88</v>
@@ -6362,13 +7399,13 @@
       <c r="Q48" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R48" s="37"/>
-      <c r="S48" s="37"/>
+      <c r="R48" s="106"/>
+      <c r="S48" s="106"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
     </row>
     <row r="49" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A49" s="42"/>
+      <c r="A49" s="53"/>
       <c r="C49" s="24"/>
       <c r="D49" s="24" t="s">
         <v>90</v>
@@ -6405,13 +7442,13 @@
       <c r="Q49" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R49" s="37"/>
-      <c r="S49" s="37"/>
+      <c r="R49" s="106"/>
+      <c r="S49" s="106"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
     </row>
     <row r="50" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A50" s="42"/>
+      <c r="A50" s="53"/>
       <c r="C50" s="24"/>
       <c r="D50" s="24" t="s">
         <v>91</v>
@@ -6448,13 +7485,13 @@
       <c r="Q50" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R50" s="37"/>
-      <c r="S50" s="37"/>
+      <c r="R50" s="106"/>
+      <c r="S50" s="106"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
     </row>
     <row r="51" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A51" s="42"/>
+      <c r="A51" s="53"/>
       <c r="C51" s="24"/>
       <c r="D51" s="24" t="s">
         <v>92</v>
@@ -6491,13 +7528,13 @@
       <c r="Q51" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R51" s="37"/>
-      <c r="S51" s="37"/>
+      <c r="R51" s="106"/>
+      <c r="S51" s="106"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
     </row>
     <row r="52" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A52" s="43"/>
+      <c r="A52" s="54"/>
       <c r="C52" s="24"/>
       <c r="D52" s="24" t="s">
         <v>93</v>
@@ -6524,23 +7561,23 @@
         <v>0</v>
       </c>
       <c r="M52" s="30" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="N52" s="29" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="O52" s="20"/>
       <c r="P52" s="20"/>
       <c r="Q52" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R52" s="37"/>
-      <c r="S52" s="37"/>
+      <c r="R52" s="106"/>
+      <c r="S52" s="106"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
     </row>
     <row r="53" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A53" s="44" t="s">
+      <c r="A53" s="55" t="s">
         <v>94</v>
       </c>
       <c r="B53" s="24" t="s">
@@ -6571,14 +7608,14 @@
       <c r="Q53" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R53" s="37"/>
-      <c r="S53" s="37"/>
+      <c r="R53" s="106"/>
+      <c r="S53" s="106"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
     </row>
     <row r="54" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A54" s="44"/>
-      <c r="B54" s="45"/>
+      <c r="A54" s="55"/>
+      <c r="B54" s="56"/>
       <c r="C54" s="24" t="s">
         <v>97</v>
       </c>
@@ -6606,14 +7643,14 @@
       <c r="Q54" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R54" s="37"/>
-      <c r="S54" s="37"/>
+      <c r="R54" s="106"/>
+      <c r="S54" s="106"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
     </row>
     <row r="55" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A55" s="44"/>
-      <c r="B55" s="42"/>
+      <c r="A55" s="55"/>
+      <c r="B55" s="53"/>
       <c r="C55" s="24"/>
       <c r="D55" s="24" t="s">
         <v>95</v>
@@ -6647,14 +7684,14 @@
       <c r="Q55" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R55" s="37"/>
-      <c r="S55" s="37"/>
+      <c r="R55" s="106"/>
+      <c r="S55" s="106"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
     </row>
     <row r="56" spans="1:21" ht="32.1" customHeight="1">
-      <c r="A56" s="44"/>
-      <c r="B56" s="43"/>
+      <c r="A56" s="55"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="24"/>
       <c r="D56" s="24" t="s">
         <v>96</v>
@@ -6688,8 +7725,8 @@
       <c r="Q56" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="R56" s="37"/>
-      <c r="S56" s="37"/>
+      <c r="R56" s="106"/>
+      <c r="S56" s="106"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
     </row>
@@ -6717,11 +7754,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A798CEB9-3A0E-4BA5-8025-D346E49E7C88}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="26.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="49.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="49.25" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.25" customWidth="1"/>
     <col min="5" max="5" width="31.75" bestFit="1" customWidth="1"/>
@@ -6732,280 +7769,346 @@
         <v>112</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>110</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="48"/>
+      <c r="B3" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="48"/>
+      <c r="B4" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="48"/>
+      <c r="B5" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>504</v>
+      </c>
+      <c r="E6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="49"/>
+      <c r="B7" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="49"/>
+      <c r="B8" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>503</v>
+      </c>
+      <c r="D8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="50"/>
+      <c r="B10" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="50"/>
+      <c r="B11" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="50"/>
+      <c r="B12" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="52"/>
+      <c r="B14" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="52"/>
+      <c r="B15" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="52"/>
+      <c r="B16" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="52"/>
+      <c r="B17" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="51"/>
+      <c r="B19" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="51"/>
+      <c r="B20" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="51"/>
+      <c r="B21" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>502</v>
+      </c>
+      <c r="E21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="51"/>
+      <c r="B22" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="E22" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="51"/>
+      <c r="B23" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="C24" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="73" t="s">
-        <v>301</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="73"/>
-      <c r="B3" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="73"/>
-      <c r="B4" s="69" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="69" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="73"/>
-      <c r="B5" s="69" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="74" t="s">
+      <c r="E24" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="47"/>
+      <c r="B25" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="E25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="47"/>
+      <c r="B26" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="47"/>
+      <c r="B27" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="47"/>
+      <c r="B28" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="47"/>
+      <c r="B29" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="B6" s="70" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="70"/>
-      <c r="D6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="74"/>
-      <c r="B7" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="74"/>
-      <c r="B8" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="75" t="s">
-        <v>303</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="75"/>
-      <c r="B10" s="71" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="75"/>
-      <c r="B11" s="71" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="71" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="75"/>
-      <c r="B12" s="71" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="71" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="76" t="s">
-        <v>304</v>
-      </c>
-      <c r="B13" s="77" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="76"/>
-      <c r="B14" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="77" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="76"/>
-      <c r="B15" s="77" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="77" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="76"/>
-      <c r="B16" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="77" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="76"/>
-      <c r="B17" s="77" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="76"/>
-      <c r="B18" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="77" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="78" t="s">
-        <v>305</v>
-      </c>
-      <c r="B19" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="72" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="78"/>
-      <c r="B20" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="72" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="78"/>
-      <c r="B21" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="78"/>
-      <c r="B22" s="72" t="s">
+      <c r="C29" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="D29" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="E22" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="78"/>
-      <c r="B23" s="72" t="s">
-        <v>151</v>
-      </c>
-      <c r="C23" s="72"/>
-      <c r="E23" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="78"/>
-      <c r="B24" s="72" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="3" t="s">
-        <v>156</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A24:A29"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A13:A17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7029,126 +8132,126 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="8"/>
     </row>
     <row r="3" spans="2:10" ht="82.5">
-      <c r="B3" s="46" t="s">
-        <v>170</v>
+      <c r="B3" s="57" t="s">
+        <v>164</v>
       </c>
       <c r="C3" s="10">
         <v>109</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="12" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="46"/>
+      <c r="B4" s="57"/>
       <c r="C4" s="10">
         <v>110</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="12" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="66">
-      <c r="B5" s="46"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="10">
         <v>110</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="12" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="2:10" ht="33">
-      <c r="B6" s="46"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="10">
         <v>112</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="46"/>
+      <c r="B7" s="57"/>
       <c r="C7" s="10">
         <v>111</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -7156,539 +8259,539 @@
     </row>
     <row r="9" spans="2:10">
       <c r="B9" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="50">
+      <c r="B10" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="61">
         <v>112</v>
       </c>
-      <c r="D10" s="53" t="s">
-        <v>189</v>
+      <c r="D10" s="64" t="s">
+        <v>183</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F10" s="10">
         <v>250.1</v>
       </c>
-      <c r="G10" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H10" s="57"/>
+      <c r="G10" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H10" s="68"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="48"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="54"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="65"/>
       <c r="E11" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F11" s="10">
         <v>226</v>
       </c>
-      <c r="G11" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="57"/>
+      <c r="G11" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="68"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="48"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="54"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="65"/>
       <c r="E12" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F12" s="9">
         <v>246.3</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="48"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="54"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="65"/>
       <c r="E13" s="9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F13" s="9">
         <v>226</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H13" s="10"/>
       <c r="J13" s="15" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="49.5">
-      <c r="B14" s="48"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="54"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F14" s="9">
         <v>225.8</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="48"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="55"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="66"/>
       <c r="E15" s="9" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F15" s="9">
         <v>251.8</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="48"/>
-      <c r="C16" s="50">
+      <c r="B16" s="59"/>
+      <c r="C16" s="61">
         <v>112</v>
       </c>
-      <c r="D16" s="53" t="s">
-        <v>201</v>
+      <c r="D16" s="64" t="s">
+        <v>195</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F16" s="9">
         <v>237.5</v>
       </c>
-      <c r="G16" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H16" s="57"/>
+      <c r="G16" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="68"/>
     </row>
     <row r="17" spans="2:10" ht="33">
-      <c r="B17" s="48"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="54"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="65"/>
       <c r="E17" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F17" s="9">
         <v>248</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="48"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="55"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="66"/>
       <c r="E18" s="9" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F18" s="9">
         <v>237.5</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="48"/>
-      <c r="C19" s="50">
+      <c r="B19" s="59"/>
+      <c r="C19" s="61">
         <v>111</v>
       </c>
-      <c r="D19" s="58" t="s">
-        <v>207</v>
+      <c r="D19" s="69" t="s">
+        <v>201</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F19" s="9">
         <v>216.6</v>
       </c>
-      <c r="G19" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="57"/>
+      <c r="G19" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="68"/>
     </row>
     <row r="20" spans="2:10" ht="33">
-      <c r="B20" s="48"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="70"/>
       <c r="E20" s="9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F20" s="9">
         <v>215.6</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H20" s="10"/>
       <c r="J20" s="6" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="48"/>
-      <c r="C21" s="50">
+      <c r="B21" s="59"/>
+      <c r="C21" s="61">
         <v>113</v>
       </c>
-      <c r="D21" s="53" t="s">
-        <v>212</v>
+      <c r="D21" s="64" t="s">
+        <v>206</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F21" s="9"/>
-      <c r="G21" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21" s="57"/>
+      <c r="G21" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="68"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="48"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="54"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="65"/>
       <c r="E22" s="9" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F22" s="9"/>
-      <c r="G22" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="57"/>
+      <c r="G22" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="68"/>
       <c r="J22" s="6" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="48"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="54"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="10" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="48"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="54"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="65"/>
       <c r="E24" s="9" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="2:10" ht="33">
-      <c r="B25" s="48"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="54"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="65"/>
       <c r="E25" s="9" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="16" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="48"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="54"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="65"/>
       <c r="E26" s="9" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="48"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="54"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="65"/>
       <c r="E27" s="9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H27" s="10"/>
       <c r="J27" s="6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="48"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="55"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="66"/>
       <c r="E28" s="9" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H28" s="10"/>
       <c r="J28" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="59"/>
+      <c r="C29" s="61">
+        <v>114</v>
+      </c>
+      <c r="D29" s="64" t="s">
+        <v>224</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="68"/>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="59"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="71" t="s">
+        <v>227</v>
+      </c>
+      <c r="H30" s="72"/>
+      <c r="I30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="59"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="59"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="9" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="48"/>
-      <c r="C29" s="50">
+      <c r="F32" s="9"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="74"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="59"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="59"/>
+      <c r="C34" s="61">
         <v>114</v>
       </c>
-      <c r="D29" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="D34" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" s="48"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="60" t="s">
+      <c r="F34" s="9"/>
+      <c r="G34" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" s="68"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="59"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="H30" s="61"/>
-      <c r="I30" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31" s="48"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="9" t="s">
+      <c r="F35" s="9"/>
+      <c r="G35" s="71" t="s">
+        <v>227</v>
+      </c>
+      <c r="H35" s="72"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="59"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="63"/>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32" s="48"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="9" t="s">
+      <c r="F36" s="9"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="74"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="59"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="63"/>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="48"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="9" t="s">
+      <c r="F37" s="9"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="74"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="59"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="65"/>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="48"/>
-      <c r="C34" s="50">
-        <v>114</v>
-      </c>
-      <c r="D34" s="53" t="s">
+      <c r="F38" s="9"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="74"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="59"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="F39" s="9"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="74"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="60"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H34" s="57"/>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="48"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="60" t="s">
-        <v>233</v>
-      </c>
-      <c r="H35" s="61"/>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="48"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="63"/>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="48"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="63"/>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="48"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="63"/>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="48"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="63"/>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="49"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="9" t="s">
-        <v>244</v>
-      </c>
       <c r="F40" s="9"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="65"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="76"/>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="17"/>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B43" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="C43" s="50">
+      <c r="B43" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" s="61">
         <v>112</v>
       </c>
-      <c r="D43" s="66" t="s">
-        <v>246</v>
+      <c r="D43" s="77" t="s">
+        <v>240</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="46"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="67"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="78"/>
       <c r="E44" s="9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="9" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -7697,67 +8800,67 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="C47" s="50">
+      <c r="B47" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="C47" s="61">
         <v>114</v>
       </c>
-      <c r="D47" s="66" t="s">
-        <v>252</v>
+      <c r="D47" s="77" t="s">
+        <v>246</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="46"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="68"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="79"/>
       <c r="E48" s="10" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="46"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="67"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="78"/>
       <c r="E49" s="10" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H49" s="10"/>
     </row>
@@ -7815,10 +8918,2259 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26D5955-1882-400F-A51D-B0D7429C9C4A}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F5CE3A-6232-49DB-88AC-2A58817E14FD}">
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="3" width="9" style="88"/>
+    <col min="4" max="4" width="16.5" style="88" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="88" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="89" customWidth="1"/>
+    <col min="7" max="7" width="137.5" style="90" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="82" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="82"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5">
+      <c r="A1" s="80" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>319</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>321</v>
+      </c>
+      <c r="F1" s="81" t="s">
+        <v>322</v>
+      </c>
+      <c r="G1" s="80" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="83" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F2" s="86"/>
+      <c r="G2" s="87" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="83"/>
+      <c r="B3" s="85" t="s">
+        <v>330</v>
+      </c>
+      <c r="C3" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E3" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F3" s="86"/>
+      <c r="G3" s="87" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="83"/>
+      <c r="B4" s="85" t="s">
+        <v>333</v>
+      </c>
+      <c r="C4" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4" s="86"/>
+      <c r="G4" s="87" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="83"/>
+      <c r="B5" s="85" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" s="85" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="86" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="87" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="83"/>
+      <c r="B6" s="85" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" s="85" t="s">
+        <v>340</v>
+      </c>
+      <c r="E6" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F6" s="86"/>
+      <c r="G6" s="87" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="83"/>
+      <c r="B7" s="85" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D7" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E7" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F7" s="86"/>
+      <c r="G7" s="87" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="83"/>
+      <c r="B8" s="84" t="s">
+        <v>344</v>
+      </c>
+      <c r="C8" s="83" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="87" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="83"/>
+      <c r="B9" s="85" t="s">
+        <v>347</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D9" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F9" s="86"/>
+      <c r="G9" s="87" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="83"/>
+      <c r="B10" s="85" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>350</v>
+      </c>
+      <c r="E10" s="85" t="s">
+        <v>351</v>
+      </c>
+      <c r="F10" s="86" t="s">
+        <v>352</v>
+      </c>
+      <c r="G10" s="87" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="83"/>
+      <c r="B11" s="85" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="85" t="s">
+        <v>351</v>
+      </c>
+      <c r="D11" s="85" t="s">
+        <v>351</v>
+      </c>
+      <c r="E11" s="85" t="s">
+        <v>351</v>
+      </c>
+      <c r="F11" s="86" t="s">
+        <v>355</v>
+      </c>
+      <c r="G11" s="87" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="83"/>
+      <c r="B12" s="85" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D12" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F12" s="86" t="s">
+        <v>357</v>
+      </c>
+      <c r="G12" s="87" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="83" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D14" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E14" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="86"/>
+      <c r="G14" s="87" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="83"/>
+      <c r="B15" s="85" t="s">
+        <v>362</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="87"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="83"/>
+      <c r="B16" s="85" t="s">
+        <v>363</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F16" s="86"/>
+      <c r="G16" s="87" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="83"/>
+      <c r="B17" s="85" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" s="86"/>
+      <c r="G17" s="87" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="83"/>
+      <c r="B18" s="85" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="85"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="87" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="83"/>
+      <c r="B19" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="C19" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D19" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E19" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F19" s="86"/>
+      <c r="G19" s="87" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="83"/>
+      <c r="B20" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D20" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E20" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F20" s="86"/>
+      <c r="G20" s="87" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="83"/>
+      <c r="B21" s="85" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E21" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" s="86"/>
+      <c r="G21" s="87"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="83"/>
+      <c r="B22" s="85" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" s="86"/>
+      <c r="G22" s="87"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="83"/>
+      <c r="B23" s="85" t="s">
+        <v>373</v>
+      </c>
+      <c r="C23" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D23" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E23" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" s="86"/>
+      <c r="G23" s="87" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="83"/>
+      <c r="B24" s="85" t="s">
+        <v>375</v>
+      </c>
+      <c r="C24" s="85" t="s">
+        <v>376</v>
+      </c>
+      <c r="D24" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="86"/>
+      <c r="G24" s="87" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="83"/>
+      <c r="B25" s="85" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D25" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E25" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="83"/>
+      <c r="B26" s="85" t="s">
+        <v>380</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D26" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E26" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F26" s="86"/>
+      <c r="G26" s="87" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="83"/>
+      <c r="B27" s="85" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D27" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F27" s="86"/>
+      <c r="G27" s="87" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="83"/>
+      <c r="B28" s="85" t="s">
+        <v>383</v>
+      </c>
+      <c r="C28" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D28" s="85" t="s">
+        <v>350</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>351</v>
+      </c>
+      <c r="F28" s="86"/>
+      <c r="G28" s="87"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="91" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30" s="92" t="s">
+        <v>385</v>
+      </c>
+      <c r="C30" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D30" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E30" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F30" s="86" t="s">
+        <v>386</v>
+      </c>
+      <c r="G30" s="87" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="93"/>
+      <c r="B31" s="85" t="s">
+        <v>388</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>376</v>
+      </c>
+      <c r="D31" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="86" t="s">
+        <v>389</v>
+      </c>
+      <c r="G31" s="87" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="83" t="s">
+        <v>391</v>
+      </c>
+      <c r="B33" s="84" t="s">
+        <v>392</v>
+      </c>
+      <c r="C33" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D33" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E33" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" s="86" t="s">
+        <v>393</v>
+      </c>
+      <c r="G33" s="87" t="s">
+        <v>394</v>
+      </c>
+      <c r="H33" s="82" t="s">
+        <v>395</v>
+      </c>
+      <c r="I33" s="82" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="83"/>
+      <c r="B34" s="85" t="s">
+        <v>397</v>
+      </c>
+      <c r="C34" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D34" s="85" t="s">
+        <v>398</v>
+      </c>
+      <c r="E34" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F34" s="86" t="s">
+        <v>399</v>
+      </c>
+      <c r="G34" s="87" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="83"/>
+      <c r="B35" s="85" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D35" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E35" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" s="86" t="s">
+        <v>402</v>
+      </c>
+      <c r="G35" s="87" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="83" t="s">
+        <v>404</v>
+      </c>
+      <c r="B37" s="85" t="s">
+        <v>405</v>
+      </c>
+      <c r="C37" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D37" s="85" t="s">
+        <v>398</v>
+      </c>
+      <c r="E37" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F37" s="86"/>
+      <c r="G37" s="87" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="83"/>
+      <c r="B38" s="85" t="s">
+        <v>407</v>
+      </c>
+      <c r="C38" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D38" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E38" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F38" s="86" t="s">
+        <v>408</v>
+      </c>
+      <c r="G38" s="87"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="83"/>
+      <c r="B39" s="84" t="s">
+        <v>409</v>
+      </c>
+      <c r="C39" s="83" t="s">
+        <v>410</v>
+      </c>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="86" t="s">
+        <v>411</v>
+      </c>
+      <c r="G39" s="87" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="83" t="s">
+        <v>413</v>
+      </c>
+      <c r="B41" s="85" t="s">
+        <v>414</v>
+      </c>
+      <c r="C41" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D41" s="85" t="s">
+        <v>415</v>
+      </c>
+      <c r="E41" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F41" s="86"/>
+      <c r="G41" s="87" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="83"/>
+      <c r="B42" s="85" t="s">
+        <v>417</v>
+      </c>
+      <c r="C42" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D42" s="85" t="s">
+        <v>418</v>
+      </c>
+      <c r="E42" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F42" s="86"/>
+      <c r="G42" s="87" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="83"/>
+      <c r="B43" s="85" t="s">
+        <v>420</v>
+      </c>
+      <c r="C43" s="83" t="s">
+        <v>410</v>
+      </c>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="87" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="83"/>
+      <c r="B44" s="85" t="s">
+        <v>422</v>
+      </c>
+      <c r="C44" s="83" t="s">
+        <v>410</v>
+      </c>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="86"/>
+      <c r="G44" s="87" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="83"/>
+      <c r="B45" s="85" t="s">
+        <v>423</v>
+      </c>
+      <c r="C45" s="85" t="s">
+        <v>376</v>
+      </c>
+      <c r="D45" s="85" t="s">
+        <v>424</v>
+      </c>
+      <c r="E45" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="86" t="s">
+        <v>425</v>
+      </c>
+      <c r="G45" s="87" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="83"/>
+      <c r="B46" s="85" t="s">
+        <v>427</v>
+      </c>
+      <c r="C46" s="85" t="s">
+        <v>376</v>
+      </c>
+      <c r="D46" s="85" t="s">
+        <v>424</v>
+      </c>
+      <c r="E46" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="86" t="s">
+        <v>428</v>
+      </c>
+      <c r="G46" s="87" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="83"/>
+      <c r="B47" s="85" t="s">
+        <v>430</v>
+      </c>
+      <c r="C47" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D47" s="85" t="s">
+        <v>415</v>
+      </c>
+      <c r="E47" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="86"/>
+      <c r="G47" s="87" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="83"/>
+      <c r="B48" s="84" t="s">
+        <v>432</v>
+      </c>
+      <c r="C48" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D48" s="85" t="s">
+        <v>398</v>
+      </c>
+      <c r="E48" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F48" s="86"/>
+      <c r="G48" s="87" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="B50" s="84" t="s">
+        <v>435</v>
+      </c>
+      <c r="C50" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D50" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="E50" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F50" s="86"/>
+      <c r="G50" s="87"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="83"/>
+      <c r="B51" s="85" t="s">
+        <v>437</v>
+      </c>
+      <c r="C51" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D51" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="E51" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F51" s="86"/>
+      <c r="G51" s="87" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="83"/>
+      <c r="B52" s="85" t="s">
+        <v>439</v>
+      </c>
+      <c r="C52" s="83" t="s">
+        <v>410</v>
+      </c>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="86"/>
+      <c r="G52" s="87" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="83"/>
+      <c r="B53" s="85" t="s">
+        <v>441</v>
+      </c>
+      <c r="C53" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D53" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="E53" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F53" s="86"/>
+      <c r="G53" s="87" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="83"/>
+      <c r="B54" s="85" t="s">
+        <v>443</v>
+      </c>
+      <c r="C54" s="83" t="s">
+        <v>410</v>
+      </c>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="86"/>
+      <c r="G54" s="87"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="83"/>
+      <c r="B55" s="85" t="s">
+        <v>444</v>
+      </c>
+      <c r="C55" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D55" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="E55" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F55" s="94" t="s">
+        <v>445</v>
+      </c>
+      <c r="G55" s="95" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="83"/>
+      <c r="B56" s="85" t="s">
+        <v>447</v>
+      </c>
+      <c r="C56" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D56" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="E56" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F56" s="96"/>
+      <c r="G56" s="97"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="83"/>
+      <c r="B57" s="85" t="s">
+        <v>448</v>
+      </c>
+      <c r="C57" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D57" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="E57" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F57" s="86" t="s">
+        <v>449</v>
+      </c>
+      <c r="G57" s="87"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="83"/>
+      <c r="B58" s="84" t="s">
+        <v>450</v>
+      </c>
+      <c r="C58" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D58" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="E58" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F58" s="86" t="s">
+        <v>451</v>
+      </c>
+      <c r="G58" s="87"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="83"/>
+      <c r="B59" s="85" t="s">
+        <v>452</v>
+      </c>
+      <c r="C59" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D59" s="85" t="s">
+        <v>418</v>
+      </c>
+      <c r="E59" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F59" s="86" t="s">
+        <v>453</v>
+      </c>
+      <c r="G59" s="87" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="31.5">
+      <c r="A61" s="85" t="s">
+        <v>455</v>
+      </c>
+      <c r="B61" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="C61" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D61" s="85" t="s">
+        <v>457</v>
+      </c>
+      <c r="E61" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="F61" s="86" t="s">
+        <v>458</v>
+      </c>
+      <c r="G61" s="98" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="83" t="s">
+        <v>460</v>
+      </c>
+      <c r="B63" s="84" t="s">
+        <v>461</v>
+      </c>
+      <c r="C63" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D63" s="85" t="s">
+        <v>462</v>
+      </c>
+      <c r="E63" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F63" s="86"/>
+      <c r="G63" s="87" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="83"/>
+      <c r="B64" s="84" t="s">
+        <v>464</v>
+      </c>
+      <c r="C64" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D64" s="85" t="s">
+        <v>462</v>
+      </c>
+      <c r="E64" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F64" s="86"/>
+      <c r="G64" s="87" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="83"/>
+      <c r="B65" s="84" t="s">
+        <v>466</v>
+      </c>
+      <c r="C65" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="D65" s="85" t="s">
+        <v>462</v>
+      </c>
+      <c r="E65" s="85" t="s">
+        <v>331</v>
+      </c>
+      <c r="F65" s="86"/>
+      <c r="G65" s="87" t="s">
+        <v>467</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A41:A48"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="A50:A59"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A14:A28"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="C39:E39"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22DF0E79-C3BC-407E-806E-F0516C601941}">
+  <dimension ref="B1:N49"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="2.25" style="6" customWidth="1"/>
+    <col min="2" max="2" width="9" style="15"/>
+    <col min="3" max="3" width="9" style="5"/>
+    <col min="4" max="4" width="0.875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9" style="15"/>
+    <col min="6" max="6" width="9" style="99"/>
+    <col min="7" max="7" width="6.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="10" style="5" customWidth="1"/>
+    <col min="9" max="9" width="9" style="99"/>
+    <col min="10" max="10" width="9.5" style="99" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.75" style="6" customWidth="1"/>
+    <col min="12" max="12" width="9" style="5"/>
+    <col min="13" max="16384" width="9" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" s="5" customFormat="1">
+      <c r="B1" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14">
+      <c r="B2" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="99">
+        <v>258.2</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" s="99">
+        <v>250.1</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I2" s="99">
+        <f>C2-F2</f>
+        <v>8.0999999999999943</v>
+      </c>
+      <c r="J2" s="99">
+        <v>49</v>
+      </c>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="99">
+        <f>F$2</f>
+        <v>250.1</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="100">
+        <v>246.3</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="I3" s="99">
+        <f>C3-F3</f>
+        <v>3.7999999999999829</v>
+      </c>
+      <c r="J3" s="99">
+        <v>27</v>
+      </c>
+      <c r="K3" s="6">
+        <v>27</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="99">
+        <f>F$2</f>
+        <v>250.1</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="99">
+        <v>226</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="I4" s="99">
+        <f>C4-F4</f>
+        <v>24.099999999999994</v>
+      </c>
+      <c r="J4" s="99">
+        <f>J3+K4</f>
+        <v>166</v>
+      </c>
+      <c r="K4" s="6">
+        <v>139</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="99">
+        <f>F$4</f>
+        <v>226</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="100">
+        <v>226</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="I5" s="99">
+        <f>C5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="99">
+        <f>K5</f>
+        <v>0.5</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="99">
+        <f>F$4</f>
+        <v>226</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="100">
+        <v>225.8</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I6" s="99">
+        <f>C6-F6</f>
+        <v>0.19999999999998863</v>
+      </c>
+      <c r="J6" s="99">
+        <f>K6</f>
+        <v>18</v>
+      </c>
+      <c r="K6" s="6">
+        <v>18</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="C7" s="99"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="C8" s="99"/>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="99">
+        <v>249.1</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" s="99">
+        <v>248</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I9" s="99">
+        <f>C9-F9</f>
+        <v>1.0999999999999943</v>
+      </c>
+      <c r="J9" s="99">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="99">
+        <v>249.1</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="99">
+        <v>237.5</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="I10" s="99">
+        <f>C10-F10</f>
+        <v>11.599999999999994</v>
+      </c>
+      <c r="J10" s="99">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="99">
+        <v>237.5</v>
+      </c>
+      <c r="E11" s="101" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="99">
+        <f>C11-0.8</f>
+        <v>236.7</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="I11" s="99">
+        <f>C11-F11</f>
+        <v>0.80000000000001137</v>
+      </c>
+      <c r="J11" s="99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="C12" s="99"/>
+      <c r="E12" s="101"/>
+      <c r="H12" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="C13" s="99"/>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="102"/>
+      <c r="E14" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" s="102"/>
+      <c r="H14" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="102"/>
+      <c r="E15" s="101" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="102"/>
+      <c r="H15" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="C16" s="102"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="102"/>
+      <c r="H16" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="C17" s="99"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="103">
+        <v>143.29</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F18" s="103">
+        <v>136.44999999999999</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="I18" s="103">
+        <f>C18-F18</f>
+        <v>6.8400000000000034</v>
+      </c>
+      <c r="J18" s="99">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="103">
+        <v>138.5</v>
+      </c>
+      <c r="E19" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="F19" s="103">
+        <v>138.4</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I19" s="103">
+        <f>C19-F19</f>
+        <v>9.9999999999994316E-2</v>
+      </c>
+      <c r="J19" s="99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="F20" s="103">
+        <v>121.08</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I20" s="103">
+        <f t="shared" ref="I20:I28" si="0">C20-F20</f>
+        <v>17.420000000000002</v>
+      </c>
+      <c r="J20" s="99">
+        <v>120</v>
+      </c>
+      <c r="K20" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C21" s="103">
+        <v>121.08</v>
+      </c>
+      <c r="E21" s="104" t="s">
+        <v>474</v>
+      </c>
+      <c r="F21" s="103">
+        <v>120.8</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="I21" s="103">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000114</v>
+      </c>
+      <c r="J21" s="99">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E22" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="F22" s="103">
+        <v>109.9</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I22" s="103">
+        <f t="shared" si="0"/>
+        <v>28.599999999999994</v>
+      </c>
+      <c r="J22" s="99">
+        <f>J20+K22</f>
+        <v>221</v>
+      </c>
+      <c r="K22" s="6">
+        <v>101</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E23" s="104" t="s">
+        <v>476</v>
+      </c>
+      <c r="F23" s="103">
+        <v>103.52</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I23" s="103">
+        <f t="shared" si="0"/>
+        <v>34.980000000000004</v>
+      </c>
+      <c r="J23" s="99">
+        <f>J22+K23</f>
+        <v>307</v>
+      </c>
+      <c r="K23" s="6">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E24" s="104" t="s">
+        <v>477</v>
+      </c>
+      <c r="F24" s="103">
+        <v>96.45</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I24" s="103">
+        <f t="shared" si="0"/>
+        <v>42.05</v>
+      </c>
+      <c r="J24" s="99">
+        <f>J23+K24</f>
+        <v>395</v>
+      </c>
+      <c r="K24" s="6">
+        <v>88</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E25" s="104" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" s="103">
+        <v>92.73</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I25" s="103">
+        <f t="shared" si="0"/>
+        <v>45.769999999999996</v>
+      </c>
+      <c r="J25" s="99">
+        <f>J24+K25</f>
+        <v>461</v>
+      </c>
+      <c r="K25" s="6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="6.75" customHeight="1">
+      <c r="C26" s="99"/>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E27" s="104" t="s">
+        <v>221</v>
+      </c>
+      <c r="F27" s="99">
+        <v>90.33</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I27" s="99">
+        <f t="shared" si="0"/>
+        <v>48.17</v>
+      </c>
+      <c r="J27" s="99">
+        <f>J25+K27</f>
+        <v>474</v>
+      </c>
+      <c r="K27" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="103">
+        <f>C$19</f>
+        <v>138.5</v>
+      </c>
+      <c r="E28" s="104" t="s">
+        <v>478</v>
+      </c>
+      <c r="F28" s="99">
+        <v>90.33</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I28" s="99">
+        <f t="shared" si="0"/>
+        <v>48.17</v>
+      </c>
+      <c r="J28" s="99">
+        <f>J27+K28</f>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="C29" s="99"/>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="C30" s="99"/>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="B31" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="99">
+        <v>99.8</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F31" s="99">
+        <v>89.9</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I31" s="99">
+        <f t="shared" ref="I31:I49" si="1">C31-F31</f>
+        <v>9.8999999999999915</v>
+      </c>
+      <c r="J31" s="99">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
+      <c r="B32" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C32" s="99">
+        <f>F$31</f>
+        <v>89.9</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="F32" s="99">
+        <v>47.98</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="I32" s="99">
+        <f t="shared" si="1"/>
+        <v>41.920000000000009</v>
+      </c>
+      <c r="J32" s="99">
+        <v>892</v>
+      </c>
+      <c r="L32" s="5">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="C33" s="99">
+        <f>F32</f>
+        <v>47.98</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F33" s="99">
+        <v>51.18</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I33" s="99">
+        <f t="shared" si="1"/>
+        <v>-3.2000000000000028</v>
+      </c>
+      <c r="J33" s="99">
+        <f>L33</f>
+        <v>63</v>
+      </c>
+      <c r="L33" s="5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" s="99">
+        <f>F$31</f>
+        <v>89.9</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="F34" s="99">
+        <v>44.55</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I34" s="99">
+        <f t="shared" si="1"/>
+        <v>45.350000000000009</v>
+      </c>
+      <c r="J34" s="99">
+        <f>J32+L34</f>
+        <v>1167</v>
+      </c>
+      <c r="L34" s="5">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="C35" s="99">
+        <f>F34</f>
+        <v>44.55</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F35" s="99">
+        <v>46.13</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I35" s="99">
+        <f t="shared" si="1"/>
+        <v>-1.5800000000000054</v>
+      </c>
+      <c r="J35" s="99">
+        <f>L35</f>
+        <v>20</v>
+      </c>
+      <c r="L35" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" s="99">
+        <f>F$31</f>
+        <v>89.9</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="F36" s="99">
+        <v>42.75</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I36" s="99">
+        <f t="shared" si="1"/>
+        <v>47.150000000000006</v>
+      </c>
+      <c r="J36" s="99">
+        <f>J34+L36</f>
+        <v>1256</v>
+      </c>
+      <c r="L36" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C37" s="99">
+        <f>F36</f>
+        <v>42.75</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="F37" s="6">
+        <v>42.1</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I37" s="99">
+        <f t="shared" si="1"/>
+        <v>0.64999999999999858</v>
+      </c>
+      <c r="J37" s="99">
+        <f>L37</f>
+        <v>10</v>
+      </c>
+      <c r="L37" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="B38" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38" s="99">
+        <f>F$31</f>
+        <v>89.9</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" s="99">
+        <v>46.3</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I38" s="99">
+        <f t="shared" si="1"/>
+        <v>43.600000000000009</v>
+      </c>
+      <c r="J38" s="99">
+        <f>J36+L38</f>
+        <v>1427</v>
+      </c>
+      <c r="L38" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="C39" s="99"/>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="99">
+        <v>73</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="F40" s="99">
+        <v>67.2</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I40" s="99">
+        <f t="shared" si="1"/>
+        <v>5.7999999999999972</v>
+      </c>
+      <c r="J40" s="99">
+        <v>177.5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="C41" s="99">
+        <f>F$40</f>
+        <v>67.2</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F41" s="99">
+        <v>67.2</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I41" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="99">
+        <v>0.5</v>
+      </c>
+      <c r="L41" s="5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="B42" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" s="99">
+        <v>58.1</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F42" s="99">
+        <v>57.9</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I42" s="99">
+        <f t="shared" si="1"/>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="J42" s="99">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="B43" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="99">
+        <f>F$40</f>
+        <v>67.2</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="F43" s="99">
+        <v>58</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I43" s="99">
+        <f t="shared" si="1"/>
+        <v>9.2000000000000028</v>
+      </c>
+      <c r="J43" s="99">
+        <f>J42+L43</f>
+        <v>205</v>
+      </c>
+      <c r="L43" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="B44" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="C44" s="99">
+        <v>58.1</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F44" s="99">
+        <v>58.2</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="I44" s="99">
+        <f t="shared" si="1"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="J44" s="99">
+        <f>L44</f>
+        <v>7</v>
+      </c>
+      <c r="L44" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="99">
+        <f>F$40</f>
+        <v>67.2</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="F45" s="99">
+        <v>58</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I45" s="99">
+        <f t="shared" si="1"/>
+        <v>9.2000000000000028</v>
+      </c>
+      <c r="J45" s="99">
+        <f>J43+L45</f>
+        <v>209</v>
+      </c>
+      <c r="L45" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
+      <c r="B46" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C46" s="99">
+        <v>58</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="F46" s="99">
+        <v>57.9</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="I46" s="99">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="J46" s="99">
+        <f>L46</f>
+        <v>7</v>
+      </c>
+      <c r="L46" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
+      <c r="B47" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="99">
+        <f>F$40</f>
+        <v>67.2</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="F47" s="99">
+        <v>55.61</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I47" s="99">
+        <f t="shared" si="1"/>
+        <v>11.590000000000003</v>
+      </c>
+      <c r="J47" s="99">
+        <f>J45+L47</f>
+        <v>296</v>
+      </c>
+      <c r="L47" s="5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="B48" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C48" s="99">
+        <v>55.61</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" s="99">
+        <v>55.15</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I48" s="99">
+        <f t="shared" si="1"/>
+        <v>0.46000000000000085</v>
+      </c>
+      <c r="J48" s="99">
+        <f>L48</f>
+        <v>5</v>
+      </c>
+      <c r="L48" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12">
+      <c r="B49" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C49" s="99">
+        <f>F$40</f>
+        <v>67.2</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="F49" s="99">
+        <v>52.2</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="I49" s="99">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J49" s="99">
+        <f>J47+L49</f>
+        <v>360</v>
+      </c>
+      <c r="L49" s="5">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E15:E16"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
